--- a/Employee_Reports_wi52/Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon Q0629.xlsx
+++ b/Employee_Reports_wi52/Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon Q0629.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -560,11 +560,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -658,11 +658,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -756,11 +756,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -805,11 +805,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -854,11 +854,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -903,11 +903,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -952,11 +952,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1001,11 +1001,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1099,11 +1099,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1136,11 +1136,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1185,11 +1185,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1235,11 +1235,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1284,11 +1284,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1321,11 +1321,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1358,11 +1358,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1407,11 +1407,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1420,6 +1420,43 @@
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>23-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1652,7 +1689,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1747,7 +1784,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7902</v>
+        <v>7894</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1776,7 +1813,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7902</v>
+        <v>7894</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1842,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1834,7 +1871,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1863,7 +1900,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1892,7 +1929,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1921,7 +1958,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1950,7 +1987,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7902</v>
+        <v>7894</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1979,7 +2016,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2008,7 +2045,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2037,7 +2074,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2066,7 +2103,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2095,7 +2132,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2124,7 +2161,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2153,7 +2190,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2182,7 +2219,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2211,7 +2248,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2240,7 +2277,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2269,7 +2306,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2298,7 +2335,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2327,7 +2364,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
